--- a/deployment_assets/offerlens_bulk_offers.xlsx
+++ b/deployment_assets/offerlens_bulk_offers.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multi-Tier" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,24 +446,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="62" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="64" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
     <col width="46" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -638,7 +639,7 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Up to Rs 15,000 instant discount on iPhone, MacBook, iPad, Watch and Pods. EMI transactions.</t>
+          <t>Up to Rs 15,000 instant discount on iPhone, MacBook, iPad, Watch and Pods. EMI transactions only.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -935,7 +936,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10% instant discount on Flipkart, EMI transactions only. Cap Rs 750 on mobiles, Rs 1,000 other categories.</t>
+          <t>10% instant discount on Flipkart. EMI transactions only. Cap Rs 750 on mobiles, Rs 1,000 other categories.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -994,7 +995,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10% instant discount on Amazon, EMI transactions only. Cap Rs 1,000 per transaction, Rs 4,000 per card.</t>
+          <t>10% instant discount on Amazon. EMI transactions only. Cap Rs 1,000 per transaction, Rs 4,000 per card.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1245,6 +1246,437 @@
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>2027-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Swiggy</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6% off food orders on Swiggy. Once per card per week. Not valid on AU co-branded or corporate cards.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>AUCC60</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.swiggy.com</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/5f4f7db2-24fd-4904-bec7-0820c17de756/generic/swiggy</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Zomato</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Flat 3% off food orders on Zomato. Can be availed multiple times a month.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>AUCC3</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zomato.com</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/dc8b79db-838b-447b-8ac9-d5d36a264595/generic/zomato</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Behrouz Biryani</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Dining</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card, Debit Card</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Up to 30% off on Behrouz Biryani via the EatSure app.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.behrouzbiryani.com</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/b7a2623d-c7b5-4336-a33c-21c9c5d10500/generic/behrouz-biryani</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PVR INOX</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Flat Rs 125 off movie tickets at PVR INOX. Once per card per month, movie tickets only.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pvrcinemas.com</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/1bf349b7-46dd-4dd4-9d41-fec5a404544c/generic/pvr-inox</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BookMyShow</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Debit Card</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Buy one get one free on movie and non-movie tickets with AU ivy Debit Card. Minimum two tickets. 6 times per month on movies, twice on non-movies.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://in.bookmyshow.com</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/e642a7d3-8ebf-472c-9ccb-5aea45519fb9/generic/bookmyshow-</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BigBasket</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Debit Card</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15% off on BigBasket with AU ivy and 'M' Circle Debit Cards. Valid 1st to 25th of each month, once per card during the offer period.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>AUDC15</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bigbasket.com</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/02dcec10-5bd2-480c-a284-9d4e79f2ff61/generic/bigbasket</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Netmeds</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card, Debit Card</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Additional 8% off medicines at Netmeds, on top of the standard 12% platform discount.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netmeds.com</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/74700860-ef2d-46d9-8036-cec4d84bb0e0/generic/netmeds</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -1259,16 +1691,764 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="56" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Bank Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tier Discount</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tier Cap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tier Min Order</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Coupon Code</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Key Restriction</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Merchant URL</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Offer Source</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Valid Until</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MakeMyTrip</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Up to 12% off</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Flight</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>MMTAU</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Valid on bookings made on TUESDAYS only. Once per card per month.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.makemytrip.com</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/4b935cd6-a71e-4bff-8faf-c31a3ea78407/generic/makemytrip</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Hotel</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>EaseMyTrip</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Up to 12% off</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Flight</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Valid on bookings made on THURSDAYS only. Once per card per month.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.easemytrip.com</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/42500c6e-ef10-4b36-b537-79ffb2f3443b/generic/easemytrip</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>International Flight</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Hotel</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>International Hotel</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ixigo</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Up to 12% off</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Flight</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Valid on bookings made on SUNDAYS only. Once per card per month.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ixigo.com</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/16614916-ba63-41f8-be95-42f4200e9fac/generic/ixigo</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>International Flight</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Hotel</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>International Hotel</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Yatra</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Up to Rs 10,000 off</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Flight - 1 ticket</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Flat Rs 799</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Once per card per month. Not valid on cards starting 406977503 or 653062913.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yatra.com</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/0a577abd-7dc0-4d48-a626-00b4376f8895/generic/yatra</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Flight - 2 tickets</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Flat Rs 1,598</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Domestic Flight - 3 tickets</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Flat Rs 2,397</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>International Flight - under Rs 30,000</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Flat Rs 2,000</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>International Flight - Rs 30,000+</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Zepto</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>AU Bank</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Up to Rs 1,000 off</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Grocery</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Flat Rs 50</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>ZEPAUCC (grocery) / ZEPAUHV (electronics)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Once per card per month.</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zeptonow.com</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://offers.au.bank.in/offers/offer-details/bb0b8fda-486b-4821-bf66-361214f4d8f7/generic/zepto</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>OfferLens bulk upload - how to use</t>
+          <t>OfferLens offer catalogue - how to use</t>
         </is>
       </c>
     </row>
@@ -1276,23 +2456,23 @@
       <c r="A2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>1. Verify every row against its Offer Source URL before uploading. These were researched automatically and may be out of date.</t>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>SHEET 'Offers' - upload these via admin panel &gt; Bulk Upload. Only the first sheet is read.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2. Upload via admin panel &gt; Bulk Upload. Only the first sheet ('Offers') is read.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>SHEET 'Multi-Tier' - enter these by hand; bulk upload cannot express per-product tiers.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>3. Column headers must not be renamed - the parser matches them by exact name.</t>
+          <t xml:space="preserve">   Use the manual form's 'Offer Breakdown' rows, one per tier.</t>
         </is>
       </c>
     </row>
@@ -1300,99 +2480,141 @@
       <c r="A6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Column notes:</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>BEFORE UPLOADING: verify each row against its Offer Source URL. These were researched</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Bank Name      Must match the Smart Wallet list exactly, or card filtering won't work.</t>
+          <t>automatically from issuer portals and terms change without notice.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Category       Must be one of the app's 7 categories, or the offer appears under no tab.</t>
-        </is>
-      </c>
+      <c r="A9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Discount Type  Percentage / Flat / Cashback.</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Column notes:</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Max Discount   The cap for 'X% off up to Rs Y'. Leave blank if uncapped.</t>
+          <t xml:space="preserve">  Bank Name      Must match the Smart Wallet list exactly, or card filtering won't work.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Min Order      Leave blank rather than 0 when there is no minimum.</t>
+          <t xml:space="preserve">  Category       Must be one of the app's 7 categories, or the offer appears under no tab.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Terms &amp; C      Left blank deliberately. Use 'Generate from offer details' per offer</t>
+          <t xml:space="preserve">  Discount Type  Percentage / Flat / Cashback.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 after upload, or write your own summary - do not paste the bank's text.</t>
+          <t xml:space="preserve">  Max Discount   The cap for 'X% off up to Rs Y'. Blank if uncapped.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Code On Site   'Yes' when a code is needed but only shown after login on the bank's site.</t>
+          <t xml:space="preserve">  Min Order      Blank rather than 0 when there is no minimum.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Offer Source   The bank's page. Merchant URL is the merchant's own site.</t>
+          <t xml:space="preserve">  Terms &amp; C      Left blank deliberately. After upload, open each offer with Edit and use</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Valid Until    YYYY-MM-DD.</t>
+          <t xml:space="preserve">                 'Generate from offer details' - do not paste the issuer's own wording.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Code On Site   'Yes' when a code is required but only shown on the issuer's site.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Not supported by bulk upload: multi-tier offer breakdowns. Add those via the manual form.</t>
+          <t xml:space="preserve">  Offer Source   The issuer's page. Merchant URL is the merchant's own site.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Valid Until    YYYY-MM-DD.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Rows 7-8 (Flipkart, Amazon) expire 31 July 2026 and are EMI-only - drop them if you launch later.</t>
+      <c r="A21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>WATCH OUT:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - BookMyShow and BigBasket (AU) are DEBIT card offers (ivy / 'M' Circle), not credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Travel offers have day-of-week limits: MakeMyTrip Tue, EaseMyTrip Thu, Ixigo Sun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Flipkart and Amazon (SBI) are EMI-only and expire 31 Jul 2026 - drop if launching later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - AU offers exclude AU co-branded and corporate cards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Most offers are once per card per month.</t>
         </is>
       </c>
     </row>
